--- a/output/Tables/2019/HIA_per_age.xlsx
+++ b/output/Tables/2019/HIA_per_age.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>448.881</v>
+        <v>416.727</v>
       </c>
       <c r="D2">
-        <v>404.061</v>
+        <v>374.538</v>
       </c>
       <c r="E2">
-        <v>493.764</v>
+        <v>458.853</v>
       </c>
       <c r="F2">
-        <v>25661.048</v>
+        <v>23812.63</v>
       </c>
       <c r="G2">
-        <v>23149.48</v>
+        <v>21448.999</v>
       </c>
       <c r="H2">
-        <v>28188.391</v>
+        <v>26183.12</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>3413367908.633</v>
+        <v>3167227690.815</v>
       </c>
       <c r="M2">
-        <v>3077051548.6</v>
+        <v>2851749199.2</v>
       </c>
       <c r="N2">
-        <v>3749312382.159</v>
+        <v>3482191103.47</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>862.102</v>
+        <v>821.5069999999999</v>
       </c>
       <c r="D3">
-        <v>785.114</v>
+        <v>746.389</v>
       </c>
       <c r="E3">
-        <v>938.76</v>
+        <v>896.313</v>
       </c>
       <c r="F3">
-        <v>40127.176</v>
+        <v>38185.273</v>
       </c>
       <c r="G3">
-        <v>36682.29</v>
+        <v>34838.692</v>
       </c>
       <c r="H3">
-        <v>43567.89</v>
+        <v>41532.225</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5335608852.862</v>
+        <v>5077860021.724</v>
       </c>
       <c r="M3">
-        <v>4877364553.002</v>
+        <v>4631649730.477</v>
       </c>
       <c r="N3">
-        <v>5797541661.361</v>
+        <v>5526850894.926</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>2289.453</v>
+        <v>2178.512</v>
       </c>
       <c r="D4">
-        <v>2096.655</v>
+        <v>1986.53</v>
       </c>
       <c r="E4">
-        <v>2482.392</v>
+        <v>2369.588</v>
       </c>
       <c r="F4">
-        <v>84986.338</v>
+        <v>80848.99400000001</v>
       </c>
       <c r="G4">
-        <v>77980.10799999999</v>
+        <v>73885.664</v>
       </c>
       <c r="H4">
-        <v>92004.262</v>
+        <v>87816.584</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>11306582001.299</v>
+        <v>10756685432.884</v>
       </c>
       <c r="M4">
-        <v>10373718157.555</v>
+        <v>9828040857.825001</v>
       </c>
       <c r="N4">
-        <v>12246881841.205</v>
+        <v>11692632278.69</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>4888.182</v>
+        <v>4571.403</v>
       </c>
       <c r="D5">
-        <v>4509.408</v>
+        <v>4206.265</v>
       </c>
       <c r="E5">
-        <v>5268.584</v>
+        <v>4938.17</v>
       </c>
       <c r="F5">
-        <v>131630.18</v>
+        <v>122801.801</v>
       </c>
       <c r="G5">
-        <v>121868.876</v>
+        <v>113414.078</v>
       </c>
       <c r="H5">
-        <v>141394.04</v>
+        <v>132190.58</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>17507786244.215</v>
+        <v>16333831305.712</v>
       </c>
       <c r="M5">
-        <v>16202173936.34</v>
+        <v>15079090167.09</v>
       </c>
       <c r="N5">
-        <v>18810623809.353</v>
+        <v>17590292757.256</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>10426.88</v>
+        <v>9456.607</v>
       </c>
       <c r="D6">
-        <v>9655.201999999999</v>
+        <v>8722.291999999999</v>
       </c>
       <c r="E6">
-        <v>11199.853</v>
+        <v>10192.7</v>
       </c>
       <c r="F6">
-        <v>178176.338</v>
+        <v>161424.214</v>
       </c>
       <c r="G6">
-        <v>165600.046</v>
+        <v>149425.569</v>
       </c>
       <c r="H6">
-        <v>190792.755</v>
+        <v>173488.161</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>23697957726.828</v>
+        <v>21469424871.292</v>
       </c>
       <c r="M6">
-        <v>22021214703.766</v>
+        <v>19870606301.046</v>
       </c>
       <c r="N6">
-        <v>25374444613.86</v>
+        <v>23073329326.932</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>16762.317</v>
+        <v>14838.039</v>
       </c>
       <c r="D7">
-        <v>15372.847</v>
+        <v>13517.205</v>
       </c>
       <c r="E7">
-        <v>18151.877</v>
+        <v>16161.591</v>
       </c>
       <c r="F7">
-        <v>124304.27</v>
+        <v>108625.271</v>
       </c>
       <c r="G7">
-        <v>115267.277</v>
+        <v>100247.982</v>
       </c>
       <c r="H7">
-        <v>133335.387</v>
+        <v>117007.692</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>16528458707.039</v>
+        <v>14444001441.575</v>
       </c>
       <c r="M7">
-        <v>15334222716.125</v>
+        <v>13334824823.842</v>
       </c>
       <c r="N7">
-        <v>17728714613.48</v>
+        <v>15555540264.055</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>22822.878</v>
+        <v>19076.967</v>
       </c>
       <c r="D8">
-        <v>20290.443</v>
+        <v>16793.435</v>
       </c>
       <c r="E8">
-        <v>25355.627</v>
+        <v>21360.991</v>
       </c>
       <c r="F8">
-        <v>19973.951</v>
+        <v>16595.927</v>
       </c>
       <c r="G8">
-        <v>16877.026</v>
+        <v>13804.344</v>
       </c>
       <c r="H8">
-        <v>23083.128</v>
+        <v>19395.64</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2656295622.175</v>
+        <v>2206802755.319</v>
       </c>
       <c r="M8">
-        <v>2244317322.153</v>
+        <v>1836172568.464</v>
       </c>
       <c r="N8">
-        <v>3069614965.075</v>
+        <v>2578883934.644</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>231.468</v>
+        <v>212.977</v>
       </c>
       <c r="D9">
-        <v>206.419</v>
+        <v>189.573</v>
       </c>
       <c r="E9">
-        <v>256.89</v>
+        <v>236.707</v>
       </c>
       <c r="F9">
-        <v>877.592</v>
+        <v>470.105</v>
       </c>
       <c r="G9">
-        <v>782.499</v>
+        <v>420.825</v>
       </c>
       <c r="H9">
-        <v>974.639</v>
+        <v>520.535</v>
       </c>
       <c r="I9">
-        <v>12890666.187</v>
+        <v>11220842.507</v>
       </c>
       <c r="J9">
-        <v>11501468.723</v>
+        <v>9991185.607000001</v>
       </c>
       <c r="K9">
-        <v>14299854.51</v>
+        <v>12465233.907</v>
       </c>
       <c r="L9">
-        <v>116703537.322</v>
+        <v>62519521.797</v>
       </c>
       <c r="M9">
-        <v>104060253.596</v>
+        <v>55943626.985</v>
       </c>
       <c r="N9">
-        <v>129575165.257</v>
+        <v>69236302.04799999</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>481.282</v>
+        <v>452.559</v>
       </c>
       <c r="D10">
-        <v>434.393</v>
+        <v>407.063</v>
       </c>
       <c r="E10">
-        <v>528.215</v>
+        <v>498.265</v>
       </c>
       <c r="F10">
-        <v>1503.523</v>
+        <v>1150.205</v>
       </c>
       <c r="G10">
-        <v>1358.291</v>
+        <v>1038.35</v>
       </c>
       <c r="H10">
-        <v>1650.94</v>
+        <v>1264.203</v>
       </c>
       <c r="I10">
-        <v>26799865.883</v>
+        <v>23838148.632</v>
       </c>
       <c r="J10">
-        <v>24212829.351</v>
+        <v>21466773.648</v>
       </c>
       <c r="K10">
-        <v>29452200.133</v>
+        <v>26261182.395</v>
       </c>
       <c r="L10">
-        <v>199996469.873</v>
+        <v>152953060.14</v>
       </c>
       <c r="M10">
-        <v>180571637.229</v>
+        <v>138025721.577</v>
       </c>
       <c r="N10">
-        <v>219691217.67</v>
+        <v>168163501</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1647.861</v>
+        <v>1576.677</v>
       </c>
       <c r="D11">
-        <v>1488.811</v>
+        <v>1413.648</v>
       </c>
       <c r="E11">
-        <v>1810.014</v>
+        <v>1742.101</v>
       </c>
       <c r="F11">
-        <v>4121.355</v>
+        <v>3526.233</v>
       </c>
       <c r="G11">
-        <v>3715.11</v>
+        <v>3169.701</v>
       </c>
       <c r="H11">
-        <v>4531.834</v>
+        <v>3886.398</v>
       </c>
       <c r="I11">
-        <v>91772135.52500001</v>
+        <v>83080126.991</v>
       </c>
       <c r="J11">
-        <v>82935928.38</v>
+        <v>74502795.84100001</v>
       </c>
       <c r="K11">
-        <v>100826803.598</v>
+        <v>91824731.479</v>
       </c>
       <c r="L11">
-        <v>548010254.709</v>
+        <v>468889821.649</v>
       </c>
       <c r="M11">
-        <v>494578325.582</v>
+        <v>421827428.642</v>
       </c>
       <c r="N11">
-        <v>602509122.135</v>
+        <v>516538054.096</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>3823.528</v>
+        <v>3555.26</v>
       </c>
       <c r="D12">
-        <v>3496.993</v>
+        <v>3241.807</v>
       </c>
       <c r="E12">
-        <v>4154.72</v>
+        <v>3873.156</v>
       </c>
       <c r="F12">
-        <v>6909.359</v>
+        <v>6772.844</v>
       </c>
       <c r="G12">
-        <v>6329.93</v>
+        <v>6189.38</v>
       </c>
       <c r="H12">
-        <v>7505.347</v>
+        <v>7373.196</v>
       </c>
       <c r="I12">
-        <v>213026796.361</v>
+        <v>187347769.31</v>
       </c>
       <c r="J12">
-        <v>194762852.487</v>
+        <v>170743917.641</v>
       </c>
       <c r="K12">
-        <v>231438092.679</v>
+        <v>204094388.147</v>
       </c>
       <c r="L12">
-        <v>919113332.76</v>
+        <v>900901416.4450001</v>
       </c>
       <c r="M12">
-        <v>841018384.376</v>
+        <v>822730101.881</v>
       </c>
       <c r="N12">
-        <v>997977767.778</v>
+        <v>980604393.1</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>11570.135</v>
+        <v>10338.082</v>
       </c>
       <c r="D13">
-        <v>10637.371</v>
+        <v>9439.155000000001</v>
       </c>
       <c r="E13">
-        <v>12509.299</v>
+        <v>11247.019</v>
       </c>
       <c r="F13">
-        <v>13759.138</v>
+        <v>14438.425</v>
       </c>
       <c r="G13">
-        <v>12643.543</v>
+        <v>13205.852</v>
       </c>
       <c r="H13">
-        <v>14888.457</v>
+        <v>15686.362</v>
       </c>
       <c r="I13">
-        <v>644602554.651</v>
+        <v>544797486.9119999</v>
       </c>
       <c r="J13">
-        <v>592660439.841</v>
+        <v>497707791.345</v>
       </c>
       <c r="K13">
-        <v>697214535.448</v>
+        <v>592673175.11</v>
       </c>
       <c r="L13">
-        <v>1829634863.588</v>
+        <v>1920383068.592</v>
       </c>
       <c r="M13">
-        <v>1682011926.122</v>
+        <v>1756799633.593</v>
       </c>
       <c r="N13">
-        <v>1980176564.87</v>
+        <v>2086119940.404</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>13474.561</v>
+        <v>11748.687</v>
       </c>
       <c r="D14">
-        <v>12346.089</v>
+        <v>10683.428</v>
       </c>
       <c r="E14">
-        <v>14610.713</v>
+        <v>12822.707</v>
       </c>
       <c r="F14">
-        <v>7965.662</v>
+        <v>14492.809</v>
       </c>
       <c r="G14">
-        <v>7263.037</v>
+        <v>13173.898</v>
       </c>
       <c r="H14">
-        <v>8681.614</v>
+        <v>15837.512</v>
       </c>
       <c r="I14">
-        <v>750587534.855</v>
+        <v>619184591.605</v>
       </c>
       <c r="J14">
-        <v>687778953.349</v>
+        <v>563112971.778</v>
       </c>
       <c r="K14">
-        <v>813823506.0930001</v>
+        <v>675658322.196</v>
       </c>
       <c r="L14">
-        <v>1059232396.389</v>
+        <v>1927268717.274</v>
       </c>
       <c r="M14">
-        <v>965601478.153</v>
+        <v>1751243860.516</v>
       </c>
       <c r="N14">
-        <v>1154179083.47</v>
+        <v>2106049016.705</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>8918.674000000001</v>
+        <v>7378.327</v>
       </c>
       <c r="D15">
-        <v>7839.139</v>
+        <v>6393.978</v>
       </c>
       <c r="E15">
-        <v>10010.111</v>
+        <v>8372.937</v>
       </c>
       <c r="F15">
-        <v>800.1319999999999</v>
+        <v>7797.694</v>
       </c>
       <c r="G15">
-        <v>650.793</v>
+        <v>6753.856</v>
       </c>
       <c r="H15">
-        <v>953.356</v>
+        <v>8864.641</v>
       </c>
       <c r="I15">
-        <v>496823901.628</v>
+        <v>388800084.857</v>
       </c>
       <c r="J15">
-        <v>436920031.444</v>
+        <v>337313848.435</v>
       </c>
       <c r="K15">
-        <v>557763925.545</v>
+        <v>441220195.141</v>
       </c>
       <c r="L15">
-        <v>106364010.698</v>
+        <v>1036877534.87</v>
       </c>
       <c r="M15">
-        <v>86567217.977</v>
+        <v>898015626.806</v>
       </c>
       <c r="N15">
-        <v>126741866.495</v>
+        <v>1178815820.942</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>1951.787</v>
+        <v>76.96899999999999</v>
       </c>
       <c r="D16">
-        <v>1644.918</v>
+        <v>67.215</v>
       </c>
       <c r="E16">
-        <v>2296.406</v>
+        <v>87.172</v>
       </c>
       <c r="F16">
-        <v>6580.584</v>
+        <v>46.91</v>
       </c>
       <c r="G16">
-        <v>5519.485</v>
+        <v>40.867</v>
       </c>
       <c r="H16">
-        <v>7779.228</v>
+        <v>53.264</v>
       </c>
       <c r="I16">
-        <v>28890813.119</v>
+        <v>2256171.258</v>
       </c>
       <c r="J16">
-        <v>24343265.966</v>
+        <v>1968376.177</v>
       </c>
       <c r="K16">
-        <v>33976567.704</v>
+        <v>2556885.341</v>
       </c>
       <c r="L16">
-        <v>874994707.209</v>
+        <v>6237491.4</v>
       </c>
       <c r="M16">
-        <v>734430247.4349999</v>
+        <v>5437203.16</v>
       </c>
       <c r="N16">
-        <v>1035094423.077</v>
+        <v>7085989.901</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>3338.79</v>
+        <v>234.032</v>
       </c>
       <c r="D17">
-        <v>2843.541</v>
+        <v>205.196</v>
       </c>
       <c r="E17">
-        <v>3881.182</v>
+        <v>264.039</v>
       </c>
       <c r="F17">
-        <v>9446.579</v>
+        <v>140.11</v>
       </c>
       <c r="G17">
-        <v>8008.247</v>
+        <v>122.63</v>
       </c>
       <c r="H17">
-        <v>11044.203</v>
+        <v>158.494</v>
       </c>
       <c r="I17">
-        <v>49442844.14</v>
+        <v>6861182.211</v>
       </c>
       <c r="J17">
-        <v>42088662.021</v>
+        <v>6013250.279</v>
       </c>
       <c r="K17">
-        <v>57576181.708</v>
+        <v>7746434.037</v>
       </c>
       <c r="L17">
-        <v>1256908493.784</v>
+        <v>18637078.51</v>
       </c>
       <c r="M17">
-        <v>1065125609.667</v>
+        <v>16311924.588</v>
       </c>
       <c r="N17">
-        <v>1468824204.678</v>
+        <v>21069448.695</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>4368.521</v>
+        <v>563.2809999999999</v>
       </c>
       <c r="D18">
-        <v>3782.189</v>
+        <v>495.421</v>
       </c>
       <c r="E18">
-        <v>5017.386</v>
+        <v>633.982</v>
       </c>
       <c r="F18">
-        <v>9949.815000000001</v>
+        <v>316.087</v>
       </c>
       <c r="G18">
-        <v>8539.005999999999</v>
+        <v>276.887</v>
       </c>
       <c r="H18">
-        <v>11517.252</v>
+        <v>357.095</v>
       </c>
       <c r="I18">
-        <v>64713820.485</v>
+        <v>16516143.556</v>
       </c>
       <c r="J18">
-        <v>55914716.23</v>
+        <v>14517413.332</v>
       </c>
       <c r="K18">
-        <v>74287071.97</v>
+        <v>18600481.147</v>
       </c>
       <c r="L18">
-        <v>1323287545.276</v>
+        <v>42036671.048</v>
       </c>
       <c r="M18">
-        <v>1135273739.334</v>
+        <v>36807870.448</v>
       </c>
       <c r="N18">
-        <v>1529842983.382</v>
+        <v>47461849.711</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>5686.614</v>
+        <v>1120.044</v>
       </c>
       <c r="D19">
-        <v>5026.382</v>
+        <v>1001.525</v>
       </c>
       <c r="E19">
-        <v>6393.554</v>
+        <v>1242.217</v>
       </c>
       <c r="F19">
-        <v>9333.874</v>
+        <v>583.326</v>
       </c>
       <c r="G19">
-        <v>8208.231</v>
+        <v>520.588</v>
       </c>
       <c r="H19">
-        <v>10554.205</v>
+        <v>648.294</v>
       </c>
       <c r="I19">
-        <v>84237443.898</v>
+        <v>32850985.144</v>
       </c>
       <c r="J19">
-        <v>74485210.248</v>
+        <v>29401979.323</v>
       </c>
       <c r="K19">
-        <v>94681258.079</v>
+        <v>36420187.47</v>
       </c>
       <c r="L19">
-        <v>1241098891.948</v>
+        <v>77561946.355</v>
       </c>
       <c r="M19">
-        <v>1091427702.345</v>
+        <v>69207309.44499999</v>
       </c>
       <c r="N19">
-        <v>1403245528.501</v>
+        <v>86245522.19499999</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>8235.025</v>
+        <v>2597.239</v>
       </c>
       <c r="D20">
-        <v>7411.591</v>
+        <v>2317.555</v>
       </c>
       <c r="E20">
-        <v>9092.906000000001</v>
+        <v>2889.053</v>
       </c>
       <c r="F20">
-        <v>8761.965</v>
+        <v>1274.862</v>
       </c>
       <c r="G20">
-        <v>7862.49</v>
+        <v>1142.16</v>
       </c>
       <c r="H20">
-        <v>9709.539000000001</v>
+        <v>1412.716</v>
       </c>
       <c r="I20">
-        <v>121920897.405</v>
+        <v>76159977.376</v>
       </c>
       <c r="J20">
-        <v>109754555.155</v>
+        <v>67874220.485</v>
       </c>
       <c r="K20">
-        <v>134707210.923</v>
+        <v>84748242.293</v>
       </c>
       <c r="L20">
-        <v>1165241977.011</v>
+        <v>169573207.916</v>
       </c>
       <c r="M20">
-        <v>1045149169.389</v>
+        <v>151886321.343</v>
       </c>
       <c r="N20">
-        <v>1290602568.016</v>
+        <v>187873094.349</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>5437.258</v>
+        <v>2405.22</v>
       </c>
       <c r="D21">
-        <v>4838.559</v>
+        <v>2117.774</v>
       </c>
       <c r="E21">
-        <v>6081.163</v>
+        <v>2702.447</v>
       </c>
       <c r="F21">
-        <v>2757.669</v>
+        <v>1084.676</v>
       </c>
       <c r="G21">
-        <v>2436.882</v>
+        <v>958.764</v>
       </c>
       <c r="H21">
-        <v>3099.235</v>
+        <v>1215.537</v>
       </c>
       <c r="I21">
-        <v>80518514.348</v>
+        <v>70515191.233</v>
       </c>
       <c r="J21">
-        <v>71634192.397</v>
+        <v>62151198.837</v>
       </c>
       <c r="K21">
-        <v>89921844.226</v>
+        <v>79198119.30500001</v>
       </c>
       <c r="L21">
-        <v>366575200.061</v>
+        <v>144203907.805</v>
       </c>
       <c r="M21">
-        <v>323853617.622</v>
+        <v>127555770.954</v>
       </c>
       <c r="N21">
-        <v>412327969.112</v>
+        <v>161747223.613</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>2155.382</v>
+        <v>1196.117</v>
       </c>
       <c r="D22">
-        <v>1794.829</v>
+        <v>975.552</v>
       </c>
       <c r="E22">
-        <v>2555.166</v>
+        <v>1431.069</v>
       </c>
       <c r="F22">
-        <v>144.243</v>
+        <v>410.454</v>
       </c>
       <c r="G22">
-        <v>111.566</v>
+        <v>338.039</v>
       </c>
       <c r="H22">
-        <v>180.772</v>
+        <v>488.089</v>
       </c>
       <c r="I22">
-        <v>31906548.178</v>
+        <v>35060597.364</v>
       </c>
       <c r="J22">
-        <v>26558703.613</v>
+        <v>28569944.769</v>
       </c>
       <c r="K22">
-        <v>37794850.719</v>
+        <v>41958133.161</v>
       </c>
       <c r="L22">
-        <v>19186967.579</v>
+        <v>54596585.395</v>
       </c>
       <c r="M22">
-        <v>14810810.884</v>
+        <v>44920447.282</v>
       </c>
       <c r="N22">
-        <v>24006366.264</v>
+        <v>64926309.256</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>402.184</v>
+        <v>364.35</v>
       </c>
       <c r="D23">
-        <v>347.535</v>
+        <v>317.763</v>
       </c>
       <c r="E23">
-        <v>460.616</v>
+        <v>412.716</v>
       </c>
       <c r="F23">
-        <v>1623.363</v>
+        <v>201.507</v>
       </c>
       <c r="G23">
-        <v>1400.442</v>
+        <v>175.611</v>
       </c>
       <c r="H23">
-        <v>1860.364</v>
+        <v>228.73</v>
       </c>
       <c r="I23">
-        <v>30243919.246</v>
+        <v>14277436.661</v>
       </c>
       <c r="J23">
-        <v>26149030.608</v>
+        <v>12462371.469</v>
       </c>
       <c r="K23">
-        <v>34612589.968</v>
+        <v>16185870.077</v>
       </c>
       <c r="L23">
-        <v>215887823.619</v>
+        <v>26800620.289</v>
       </c>
       <c r="M23">
-        <v>186323826.539</v>
+        <v>23358817.014</v>
       </c>
       <c r="N23">
-        <v>247712166.668</v>
+        <v>30426707.616</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>644.348</v>
+        <v>596.923</v>
       </c>
       <c r="D24">
-        <v>561.598</v>
+        <v>523.77</v>
       </c>
       <c r="E24">
-        <v>732.129</v>
+        <v>673.128</v>
       </c>
       <c r="F24">
-        <v>2143.82</v>
+        <v>577.126</v>
       </c>
       <c r="G24">
-        <v>1868.474</v>
+        <v>506.701</v>
       </c>
       <c r="H24">
-        <v>2439.804</v>
+        <v>651.71</v>
       </c>
       <c r="I24">
-        <v>48456988.146</v>
+        <v>23405407.894</v>
       </c>
       <c r="J24">
-        <v>42276049.557</v>
+        <v>20540285.667</v>
       </c>
       <c r="K24">
-        <v>55028968.612</v>
+        <v>26387185.911</v>
       </c>
       <c r="L24">
-        <v>285249093.143</v>
+        <v>76785286.87899999</v>
       </c>
       <c r="M24">
-        <v>248511303.194</v>
+        <v>67384732.102</v>
       </c>
       <c r="N24">
-        <v>324700607.839</v>
+        <v>86741974.54099999</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>955.9400000000001</v>
+        <v>891.678</v>
       </c>
       <c r="D25">
-        <v>836.7380000000001</v>
+        <v>781.169</v>
       </c>
       <c r="E25">
-        <v>1083.004</v>
+        <v>1005.834</v>
       </c>
       <c r="F25">
-        <v>2533.535</v>
+        <v>1127.032</v>
       </c>
       <c r="G25">
-        <v>2211.945</v>
+        <v>987.221</v>
       </c>
       <c r="H25">
-        <v>2877.382</v>
+        <v>1272.91</v>
       </c>
       <c r="I25">
-        <v>71896542.059</v>
+        <v>34947481.346</v>
       </c>
       <c r="J25">
-        <v>62933450.119</v>
+        <v>30624265.39</v>
       </c>
       <c r="K25">
-        <v>81482599.82099999</v>
+        <v>39447506.687</v>
       </c>
       <c r="L25">
-        <v>336966107.378</v>
+        <v>149914337.484</v>
       </c>
       <c r="M25">
-        <v>294198806.52</v>
+        <v>131325649.178</v>
       </c>
       <c r="N25">
-        <v>382612798.696</v>
+        <v>169400895.867</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>1514.418</v>
+        <v>1379.045</v>
       </c>
       <c r="D26">
-        <v>1350.086</v>
+        <v>1235.917</v>
       </c>
       <c r="E26">
-        <v>1688.644</v>
+        <v>1526.814</v>
       </c>
       <c r="F26">
-        <v>2930.577</v>
+        <v>1702.035</v>
       </c>
       <c r="G26">
-        <v>2610.459</v>
+        <v>1519.728</v>
       </c>
       <c r="H26">
-        <v>3270.774</v>
+        <v>1891.87</v>
       </c>
       <c r="I26">
-        <v>113905266.055</v>
+        <v>54069601.371</v>
       </c>
       <c r="J26">
-        <v>101483549.667</v>
+        <v>48445748.158</v>
       </c>
       <c r="K26">
-        <v>126984830.849</v>
+        <v>59862005.055</v>
       </c>
       <c r="L26">
-        <v>389951026.195</v>
+        <v>226456980.104</v>
       </c>
       <c r="M26">
-        <v>347210737.359</v>
+        <v>202225696.219</v>
       </c>
       <c r="N26">
-        <v>435020809.582</v>
+        <v>251553960.137</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>2162.381</v>
+        <v>1899.611</v>
       </c>
       <c r="D27">
-        <v>1947.109</v>
+        <v>1712.688</v>
       </c>
       <c r="E27">
-        <v>2387.461</v>
+        <v>2092.258</v>
       </c>
       <c r="F27">
-        <v>2801.379</v>
+        <v>3210.647</v>
       </c>
       <c r="G27">
-        <v>2516.722</v>
+        <v>2871.438</v>
       </c>
       <c r="H27">
-        <v>3098.76</v>
+        <v>3563.816</v>
       </c>
       <c r="I27">
-        <v>162613031.518</v>
+        <v>74452386.926</v>
       </c>
       <c r="J27">
-        <v>146368806.884</v>
+        <v>67106206.075</v>
       </c>
       <c r="K27">
-        <v>179413619.18</v>
+        <v>81954071.027</v>
       </c>
       <c r="L27">
-        <v>372727955.56</v>
+        <v>427244297.503</v>
       </c>
       <c r="M27">
-        <v>334856770.064</v>
+        <v>382152081.836</v>
       </c>
       <c r="N27">
-        <v>412288546.64</v>
+        <v>474036200.989</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>696.09</v>
+        <v>597.1799999999999</v>
       </c>
       <c r="D28">
-        <v>620.8579999999999</v>
+        <v>532.102</v>
       </c>
       <c r="E28">
-        <v>775.0940000000001</v>
+        <v>664.775</v>
       </c>
       <c r="F28">
-        <v>460.08</v>
+        <v>2522.036</v>
       </c>
       <c r="G28">
-        <v>405.411</v>
+        <v>2225.439</v>
       </c>
       <c r="H28">
-        <v>518.1369999999999</v>
+        <v>2835.42</v>
       </c>
       <c r="I28">
-        <v>52337664.788</v>
+        <v>23405680.274</v>
       </c>
       <c r="J28">
-        <v>46698636.272</v>
+        <v>20850808.862</v>
       </c>
       <c r="K28">
-        <v>58255435.575</v>
+        <v>26043589.949</v>
       </c>
       <c r="L28">
-        <v>61183221.944</v>
+        <v>335410003.482</v>
       </c>
       <c r="M28">
-        <v>53905108.468</v>
+        <v>295778769.245</v>
       </c>
       <c r="N28">
-        <v>68891012.13</v>
+        <v>377118113.408</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>27.72</v>
+        <v>22.797</v>
       </c>
       <c r="D29">
-        <v>23.339</v>
+        <v>19.03</v>
       </c>
       <c r="E29">
-        <v>32.458</v>
+        <v>26.83</v>
       </c>
       <c r="F29">
-        <v>3.109</v>
+        <v>1005.76</v>
       </c>
       <c r="G29">
-        <v>2.373</v>
+        <v>820.145</v>
       </c>
       <c r="H29">
-        <v>3.945</v>
+        <v>1214.201</v>
       </c>
       <c r="I29">
-        <v>2084753.343</v>
+        <v>893437.866</v>
       </c>
       <c r="J29">
-        <v>1753924.836</v>
+        <v>746401.481</v>
       </c>
       <c r="K29">
-        <v>2439746.072</v>
+        <v>1051096.325</v>
       </c>
       <c r="L29">
-        <v>413679.652</v>
+        <v>133790790.9</v>
       </c>
       <c r="M29">
-        <v>315199.613</v>
+        <v>109118120.741</v>
       </c>
       <c r="N29">
-        <v>524482.7439999999</v>
+        <v>161768812.895</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>164.73</v>
+        <v>154.613</v>
       </c>
       <c r="D32">
-        <v>149.002</v>
+        <v>139.014</v>
       </c>
       <c r="E32">
-        <v>180.734</v>
+        <v>170.592</v>
       </c>
       <c r="F32">
-        <v>1341.11</v>
+        <v>112.443</v>
       </c>
       <c r="G32">
-        <v>1209.463</v>
+        <v>101.091</v>
       </c>
       <c r="H32">
-        <v>1476.19</v>
+        <v>124.128</v>
       </c>
       <c r="I32">
-        <v>2774058.828</v>
+        <v>2574042.366</v>
       </c>
       <c r="J32">
-        <v>2509598.851</v>
+        <v>2314723.177</v>
       </c>
       <c r="K32">
-        <v>3043616.113</v>
+        <v>2840512.76</v>
       </c>
       <c r="L32">
-        <v>178375751.523</v>
+        <v>14954512.564</v>
       </c>
       <c r="M32">
-        <v>160839236.238</v>
+        <v>13442979.22</v>
       </c>
       <c r="N32">
-        <v>196448873.004</v>
+        <v>16525569.076</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>316.317</v>
+        <v>288.425</v>
       </c>
       <c r="D33">
-        <v>289.18</v>
+        <v>262.894</v>
       </c>
       <c r="E33">
-        <v>344.123</v>
+        <v>314.586</v>
       </c>
       <c r="F33">
-        <v>1879.63</v>
+        <v>501.935</v>
       </c>
       <c r="G33">
-        <v>1714.545</v>
+        <v>456.828</v>
       </c>
       <c r="H33">
-        <v>2049.65</v>
+        <v>547.994</v>
       </c>
       <c r="I33">
-        <v>5325955.622</v>
+        <v>4801238.867</v>
       </c>
       <c r="J33">
-        <v>4869492.105</v>
+        <v>4376254.456</v>
       </c>
       <c r="K33">
-        <v>5793345.449</v>
+        <v>5235618.436</v>
       </c>
       <c r="L33">
-        <v>250010418.542</v>
+        <v>66748776.842</v>
       </c>
       <c r="M33">
-        <v>228131385.318</v>
+        <v>60779938.401</v>
       </c>
       <c r="N33">
-        <v>272499092.233</v>
+        <v>72928849.381</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>1891.863</v>
+        <v>1666.902</v>
       </c>
       <c r="D34">
-        <v>1751.498</v>
+        <v>1535.119</v>
       </c>
       <c r="E34">
-        <v>2034.149</v>
+        <v>1800.954</v>
       </c>
       <c r="F34">
-        <v>7475.165</v>
+        <v>1765.242</v>
       </c>
       <c r="G34">
-        <v>6898.115</v>
+        <v>1624.228</v>
       </c>
       <c r="H34">
-        <v>8058.477</v>
+        <v>1908.104</v>
       </c>
       <c r="I34">
-        <v>31859543.28</v>
+        <v>27751739.015</v>
       </c>
       <c r="J34">
-        <v>29500794.537</v>
+        <v>25546925.977</v>
       </c>
       <c r="K34">
-        <v>34247475.308</v>
+        <v>29991923.15</v>
       </c>
       <c r="L34">
-        <v>994076425.516</v>
+        <v>234775138.262</v>
       </c>
       <c r="M34">
-        <v>917220419.7869999</v>
+        <v>215897420.64</v>
       </c>
       <c r="N34">
-        <v>1071859877.368</v>
+        <v>253807188.058</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>5137.993</v>
+        <v>4371.928</v>
       </c>
       <c r="D35">
-        <v>4722.507</v>
+        <v>3992.143</v>
       </c>
       <c r="E35">
-        <v>5560.34</v>
+        <v>4757.48</v>
       </c>
       <c r="F35">
-        <v>10417.782</v>
+        <v>4844.962</v>
       </c>
       <c r="G35">
-        <v>9460.699000000001</v>
+        <v>4416.422</v>
       </c>
       <c r="H35">
-        <v>11381.575</v>
+        <v>5278.868</v>
       </c>
       <c r="I35">
-        <v>86549201.09100001</v>
+        <v>72807581.669</v>
       </c>
       <c r="J35">
-        <v>79572009.75</v>
+        <v>66480163.378</v>
       </c>
       <c r="K35">
-        <v>93647094.228</v>
+        <v>79219264.344</v>
       </c>
       <c r="L35">
-        <v>1385841726.218</v>
+        <v>644464199.7180001</v>
       </c>
       <c r="M35">
-        <v>1258379709.382</v>
+        <v>587451086.6619999</v>
       </c>
       <c r="N35">
-        <v>1514137048.275</v>
+        <v>701894824.8150001</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>6416.54</v>
+        <v>5193.309</v>
       </c>
       <c r="D36">
-        <v>5670.984</v>
+        <v>4529.205</v>
       </c>
       <c r="E36">
-        <v>7170.412</v>
+        <v>5870.788</v>
       </c>
       <c r="F36">
-        <v>2133.833</v>
+        <v>6084.326</v>
       </c>
       <c r="G36">
-        <v>1741.563</v>
+        <v>5298.094</v>
       </c>
       <c r="H36">
-        <v>2533.024</v>
+        <v>6878.95</v>
       </c>
       <c r="I36">
-        <v>108069146.482</v>
+        <v>86493255.612</v>
       </c>
       <c r="J36">
-        <v>95534929.54700001</v>
+        <v>75365498.634</v>
       </c>
       <c r="K36">
-        <v>120787400.321</v>
+        <v>97741988.36</v>
       </c>
       <c r="L36">
-        <v>283727203.087</v>
+        <v>808939405.755</v>
       </c>
       <c r="M36">
-        <v>231628129.778</v>
+        <v>704404597.232</v>
       </c>
       <c r="N36">
-        <v>337104012.758</v>
+        <v>915739576.351</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>19049.559</v>
+        <v>19770.733</v>
       </c>
       <c r="D37">
-        <v>16725.041</v>
+        <v>17473.457</v>
       </c>
       <c r="E37">
-        <v>21477.241</v>
+        <v>22101.013</v>
       </c>
       <c r="F37">
-        <v>10742.403</v>
+        <v>12728.03</v>
       </c>
       <c r="G37">
-        <v>9357.040000000001</v>
+        <v>11200.259</v>
       </c>
       <c r="H37">
-        <v>12219.022</v>
+        <v>14268.591</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>1428646781.76</v>
+        <v>1692891219.641</v>
       </c>
       <c r="M37">
-        <v>1245206974.135</v>
+        <v>1491311259.628</v>
       </c>
       <c r="N37">
-        <v>1626425157.257</v>
+        <v>1898301391.015</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>20620.028</v>
+        <v>21333.761</v>
       </c>
       <c r="D38">
-        <v>18249.311</v>
+        <v>18828.061</v>
       </c>
       <c r="E38">
-        <v>23068.633</v>
+        <v>23850.964</v>
       </c>
       <c r="F38">
-        <v>9849.184999999999</v>
+        <v>11627.474</v>
       </c>
       <c r="G38">
-        <v>8647.174999999999</v>
+        <v>10215.86</v>
       </c>
       <c r="H38">
-        <v>11117.517</v>
+        <v>13055.948</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>1309554688.31</v>
+        <v>1545951784.06</v>
       </c>
       <c r="M38">
-        <v>1151105908.347</v>
+        <v>1358744024.671</v>
       </c>
       <c r="N38">
-        <v>1477609816.573</v>
+        <v>1735760034.786</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>19795.069</v>
+        <v>20868.446</v>
       </c>
       <c r="D39">
-        <v>17668.761</v>
+        <v>18512.254</v>
       </c>
       <c r="E39">
-        <v>21971.639</v>
+        <v>23238.77</v>
       </c>
       <c r="F39">
-        <v>7828.191</v>
+        <v>9383.467000000001</v>
       </c>
       <c r="G39">
-        <v>6913.931</v>
+        <v>8266.121999999999</v>
       </c>
       <c r="H39">
-        <v>8784.995000000001</v>
+        <v>10515.26</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>1041070652.669</v>
+        <v>1247942139.675</v>
       </c>
       <c r="M39">
-        <v>919703757.3049999</v>
+        <v>1099889239.916</v>
       </c>
       <c r="N39">
-        <v>1168201462.988</v>
+        <v>1398129575.847</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>19524.186</v>
+        <v>19548.872</v>
       </c>
       <c r="D40">
-        <v>17617.39</v>
+        <v>17552.654</v>
       </c>
       <c r="E40">
-        <v>21474.985</v>
+        <v>21563.918</v>
       </c>
       <c r="F40">
-        <v>5816.455</v>
+        <v>6605.953</v>
       </c>
       <c r="G40">
-        <v>5201.819</v>
+        <v>5897.526</v>
       </c>
       <c r="H40">
-        <v>6460.125</v>
+        <v>7320.931</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>773555251.494</v>
+        <v>878537350.742</v>
       </c>
       <c r="M40">
-        <v>692200650.456</v>
+        <v>784369090.3660001</v>
       </c>
       <c r="N40">
-        <v>858865890.441</v>
+        <v>973902629.145</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>23804.853</v>
+        <v>23362.224</v>
       </c>
       <c r="D41">
-        <v>21826.033</v>
+        <v>21304.248</v>
       </c>
       <c r="E41">
-        <v>25813.195</v>
+        <v>25421.963</v>
       </c>
       <c r="F41">
-        <v>4861.787</v>
+        <v>5402.421</v>
       </c>
       <c r="G41">
-        <v>4414.824</v>
+        <v>4895.623</v>
       </c>
       <c r="H41">
-        <v>5322.999</v>
+        <v>5912.761</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>646596462.2819999</v>
+        <v>718440470.847</v>
       </c>
       <c r="M41">
-        <v>587325740.705</v>
+        <v>650989283.337</v>
       </c>
       <c r="N41">
-        <v>707629285.609</v>
+        <v>785988732.928</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>16054.274</v>
+        <v>15057.862</v>
       </c>
       <c r="D42">
-        <v>14562.38</v>
+        <v>13536.82</v>
       </c>
       <c r="E42">
-        <v>17573.134</v>
+        <v>16590.103</v>
       </c>
       <c r="F42">
-        <v>1768.212</v>
+        <v>1863.556</v>
       </c>
       <c r="G42">
-        <v>1571.439</v>
+        <v>1643.756</v>
       </c>
       <c r="H42">
-        <v>1973.523</v>
+        <v>2086.584</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>235230691.543</v>
+        <v>247873485.696</v>
       </c>
       <c r="M42">
-        <v>209050200.293</v>
+        <v>218755036.369</v>
       </c>
       <c r="N42">
-        <v>262345801.189</v>
+        <v>277502049.248</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>7114.52</v>
+        <v>6262.464</v>
       </c>
       <c r="D43">
-        <v>6193.65</v>
+        <v>5317.129</v>
       </c>
       <c r="E43">
-        <v>8059.037</v>
+        <v>7213.005</v>
       </c>
       <c r="F43">
-        <v>143.901</v>
+        <v>142.858</v>
       </c>
       <c r="G43">
-        <v>114.769</v>
+        <v>109.375</v>
       </c>
       <c r="H43">
-        <v>174.732</v>
+        <v>177.394</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>19127733.449</v>
+        <v>18989408.306</v>
       </c>
       <c r="M43">
-        <v>15237633.967</v>
+        <v>14522034.137</v>
       </c>
       <c r="N43">
-        <v>23235438.301</v>
+        <v>23562344.609</v>
       </c>
     </row>
   </sheetData>
